--- a/05_Figures/F06_prediction/proteins/T3/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/d_1rm_ext/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -128,405 +128,393 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">CHORDC1</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPS17</t>
   </si>
   <si>
-    <t xml:space="preserve">CHORDC1</t>
+    <t xml:space="preserve">GLRX</t>
   </si>
   <si>
     <t xml:space="preserve">HSPB8</t>
   </si>
   <si>
+    <t xml:space="preserve">PCCB</t>
+  </si>
+  <si>
     <t xml:space="preserve">PTPA</t>
   </si>
   <si>
+    <t xml:space="preserve">BLMH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF1AX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PYGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRMT112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELOB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSBPL1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2CB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPG7</t>
+  </si>
+  <si>
     <t xml:space="preserve">AGMAT</t>
   </si>
   <si>
-    <t xml:space="preserve">BLMH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF1AX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLRX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSBPL1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PYGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOD2</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDV3</t>
   </si>
   <si>
-    <t xml:space="preserve">CLTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELOB</t>
+    <t xml:space="preserve">PDK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJC19</t>
   </si>
   <si>
     <t xml:space="preserve">ENSA</t>
   </si>
   <si>
-    <t xml:space="preserve">HAGH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVD</t>
+    <t xml:space="preserve">IRGQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHOC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR4</t>
   </si>
   <si>
     <t xml:space="preserve">PPP1R3A</t>
   </si>
   <si>
-    <t xml:space="preserve">PPP2CB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SBDS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRMT112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJC19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRGQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPG7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL3</t>
+    <t xml:space="preserve">UNC45B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS15A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STK38</t>
   </si>
   <si>
     <t xml:space="preserve">UBE2D1</t>
   </si>
   <si>
-    <t xml:space="preserve">CBR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNC45B</t>
+    <t xml:space="preserve">ACADS</t>
   </si>
   <si>
     <t xml:space="preserve">ACOT1</t>
   </si>
   <si>
-    <t xml:space="preserve">FABP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS15A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A4</t>
+    <t xml:space="preserve">AKR1C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNG12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GYG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEBP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHATL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IARS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QDPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZADH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACYP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH7A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAG3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11orf54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C12orf73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDNF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLUH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL4A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS5</t>
   </si>
   <si>
     <t xml:space="preserve">COPS6</t>
   </si>
   <si>
-    <t xml:space="preserve">ELOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNG12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPIL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSTN</t>
+    <t xml:space="preserve">COPZ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCAF6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDAH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAPH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUS</t>
   </si>
   <si>
     <t xml:space="preserve">GCLM</t>
   </si>
   <si>
+    <t xml:space="preserve">GNAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPC1</t>
+  </si>
+  <si>
     <t xml:space="preserve">GPD2</t>
   </si>
   <si>
-    <t xml:space="preserve">GYG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEBP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHATL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IARS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C3A</t>
+    <t xml:space="preserve">GRB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSK3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTZ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSD17B12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSDL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYOU1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPKAPK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLYCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUSTN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAXD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUBP1</t>
   </si>
   <si>
     <t xml:space="preserve">NUDT3</t>
   </si>
   <si>
-    <t xml:space="preserve">QDPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STK38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZADH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACYP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH7A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP2M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5F1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5F1C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAG3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOLA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11orf54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C12orf73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CES2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLUH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYSTM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCAF6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDAH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDOST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPYSL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS15L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSK3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSD17B12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSDL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYOU1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LXN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPKAPK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLYCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUSTN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NACA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NANS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAXD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUBP1</t>
-  </si>
-  <si>
     <t xml:space="preserve">PABPC4</t>
   </si>
   <si>
@@ -536,7 +524,7 @@
     <t xml:space="preserve">PCBD1</t>
   </si>
   <si>
-    <t xml:space="preserve">PCBP2</t>
+    <t xml:space="preserve">PCYT2</t>
   </si>
   <si>
     <t xml:space="preserve">PDCD5</t>
@@ -551,12 +539,6 @@
     <t xml:space="preserve">PGRMC1</t>
   </si>
   <si>
-    <t xml:space="preserve">PLIN5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMM2</t>
-  </si>
-  <si>
     <t xml:space="preserve">PNPT1</t>
   </si>
   <si>
@@ -590,6 +572,9 @@
     <t xml:space="preserve">RPL22</t>
   </si>
   <si>
+    <t xml:space="preserve">RPL27A</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPL38</t>
   </si>
   <si>
@@ -608,9 +593,6 @@
     <t xml:space="preserve">SEC23A</t>
   </si>
   <si>
-    <t xml:space="preserve">SHOC2</t>
-  </si>
-  <si>
     <t xml:space="preserve">SLC44A2</t>
   </si>
   <si>
@@ -620,13 +602,16 @@
     <t xml:space="preserve">SORD</t>
   </si>
   <si>
+    <t xml:space="preserve">STX7</t>
+  </si>
+  <si>
     <t xml:space="preserve">TACO1</t>
   </si>
   <si>
     <t xml:space="preserve">TKFC</t>
   </si>
   <si>
-    <t xml:space="preserve">TMX4</t>
+    <t xml:space="preserve">TMED1</t>
   </si>
   <si>
     <t xml:space="preserve">TPD52L2</t>
@@ -635,10 +620,10 @@
     <t xml:space="preserve">TSFM</t>
   </si>
   <si>
-    <t xml:space="preserve">TSG101</t>
-  </si>
-  <si>
     <t xml:space="preserve">UBA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE3A</t>
   </si>
   <si>
     <t xml:space="preserve">UQCRH</t>
@@ -1028,16 +1013,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.438819630465789</v>
+        <v>-0.390753830568083</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.292952252500067</v>
+        <v>-0.235683391109077</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1061,29 +1046,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.438819630465789</v>
+        <v>-0.390753830568083</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.292952252500067</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.348258706467662</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.656716417910448</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.801127961474391</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.846752935006467</v>
-      </c>
+        <v>-0.235683391109077</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1107,2206 +1084,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1.15365834955199</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.323961546014083</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.30956854035732</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.00340229227985123</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.261359754838586</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-1.22712056326884</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.202379453990539</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.40836817253826</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.597278777946215</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-2.76458816687895</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.749363314581623</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.161261628205576</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-4.8779227673935</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.26604326681625</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.286560294658294</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.901225848887181</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-2.41284825637188</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.710993692207597</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-1.58450706486917</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.47775587797798</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.0483156087128096</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.458113332060651</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.280280584611397</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.66992639705893</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.545699897018106</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.818008173293387</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.347047462265503</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-1.05587223490738</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.184177163499022</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-1.73675471240006</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-1.13134397086668</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.475874232263146</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.333195695081569</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-2.28618474978354</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-1.79723889692639</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.380368470875806</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.169049472150359</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.401202754417574</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.360942383303109</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.310728988620437</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.44312023224437</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.58643240252355</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.154802499569639</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-1.65738921470549</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.673257686161649</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.791677481999818</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.0072867729582764</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-1.27851345115429</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.073217224473116</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.670811962015184</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-2.96900894927118</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.743164287594075</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.105771506122783</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.0232208697928413</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.5957625036367</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.803496017849058</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.412281486004709</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.736808531080276</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.0365255031632048</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.911062739691031</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.548647352499528</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.469473707739179</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.858914321610664</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.633516082278096</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.0719122011641529</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.173073462449153</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.814815177517424</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.920522283682591</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.580696166952371</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.298394921903293</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.215087674210984</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.620029899252201</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.36718131534681</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.709674166449478</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.924683882522824</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-1.79637024858006</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.467422392171464</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.320673897526787</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.09043147232387</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.193343349731942</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-1.71947459593177</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.418208417345613</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.203274475274219</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.539643493674118</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-2.26723572616127</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.703924576227209</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-1.75391966070654</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.318108203829246</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0.100473011016647</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.481313138710255</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.445052991348747</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.765735413841485</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0.4660514089839</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.544141547066372</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-2.46027746149342</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-1.52619856703297</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0.249503633836692</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-1.11302184033579</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.804953586361433</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-1.44859471922659</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.88893536122664</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-1.91336990479326</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.050926163785262</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-2.00388678138554</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0.24402790814563</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.156896521568303</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-1.79598413073653</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-2.13247095571116</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.865801349889081</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.734263320463677</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-1.0315064585163</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.187249258177002</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.547014716528522</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-1.48992215788916</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.757553454729816</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.168184619614212</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-1.22915955183223</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>0.409935057501843</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>0.657634527526982</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.585008467516613</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-1.7666162046618</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-1.46009157163203</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.0122647109963359</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0.77552277383791</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.931484193761966</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-2.46069967379788</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.675827611470639</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-1.24421826724907</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-1.58862044242724</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.44404447173311</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.783067183080534</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-1.34388873758019</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-1.76665076927623</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-1.73680663166358</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.663994486571671</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-1.36244376292999</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.51500553629312</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.09646907247164</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>0.238502192599838</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-1.16293111334634</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.208401656725641</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-1.87443865246477</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-2.06416383044555</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-2.8359705355225</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-2.38567008027616</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.743845093053478</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.812569947599049</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-1.41603030390351</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.280368655642747</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>0.0882701847000498</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.582873836781324</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-1.37482709454541</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.0240740441294744</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.667966594500277</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.622679125431145</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-1.42027040916693</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.547930388977302</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.844688100421833</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-2.37957791645792</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.947668040265505</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-1.25492037191587</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.316405849124088</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.799301686826613</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-1.29997868583333</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-3.93976219319347</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.883310532847772</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.916626001651959</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.347421002821447</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.623299858900153</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.28303123058091</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.78981434964255</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0.448408911604745</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.236296641264382</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>0.553278341815026</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.799727988823815</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-1.57837340436044</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-1.13175813323762</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-1.47630533560114</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.92380750052742</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0.285882476915856</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-1.16092554807552</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.86102178818577</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-1.05556906133789</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.697968882083551</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0.11675404559156</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.0546383957823324</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-1.395142302922</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.598364763613837</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-1.77362699767805</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.958329287094794</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.839641525184573</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-1.26939567444685</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-1.38663698027623</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.3404576127488</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-1.54988171406946</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.916958472574188</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.836674353786463</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.477470582473974</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.494402863019852</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.376789434656804</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3349,7 +1126,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>10.340139885927</v>
+        <v>10.2295297167733</v>
       </c>
     </row>
     <row r="3">
@@ -3366,7 +1143,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>10.9647146299873</v>
+        <v>12.2512907359961</v>
       </c>
     </row>
     <row r="4">
@@ -3383,7 +1160,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>9.89461956106706</v>
+        <v>8.39524830342989</v>
       </c>
     </row>
     <row r="5">
@@ -3400,7 +1177,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>7.63702730006493</v>
+        <v>7.45614539586637</v>
       </c>
     </row>
     <row r="6">
@@ -3417,7 +1194,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>8.60252698827092</v>
+        <v>7.97883766647261</v>
       </c>
     </row>
     <row r="7">
@@ -3434,7 +1211,7 @@
         <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>7.22727573065158</v>
+        <v>6.73907678265305</v>
       </c>
     </row>
     <row r="8">
@@ -3451,7 +1228,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>14.5231890716832</v>
+        <v>11.5195201461025</v>
       </c>
     </row>
     <row r="9">
@@ -3468,7 +1245,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>9.52415769197346</v>
+        <v>9.42952752053672</v>
       </c>
     </row>
     <row r="10">
@@ -3485,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>5.84491919777175</v>
+        <v>3.62439252120762</v>
       </c>
     </row>
     <row r="11">
@@ -3502,7 +1279,7 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>10.7685661729843</v>
+        <v>10.2496977461933</v>
       </c>
     </row>
     <row r="12">
@@ -3519,7 +1296,7 @@
         <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>3.03064690186366</v>
+        <v>2.32621377998094</v>
       </c>
     </row>
     <row r="13">
@@ -3536,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>9.4672667489821</v>
+        <v>9.32912781748611</v>
       </c>
     </row>
     <row r="14">
@@ -3553,7 +1330,7 @@
         <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>14.8875538960907</v>
+        <v>14.5793051148776</v>
       </c>
     </row>
     <row r="15">
@@ -3570,7 +1347,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>10.9058192054264</v>
+        <v>10.5229732626846</v>
       </c>
     </row>
   </sheetData>
@@ -3629,10 +1406,10 @@
         <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928571428571429</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3646,10 +1423,10 @@
         <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="5">
@@ -3663,10 +1440,10 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -3714,10 +1491,10 @@
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="9">
@@ -3731,10 +1508,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="10">
@@ -3748,10 +1525,10 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="11">
@@ -3765,10 +1542,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="12">
@@ -3782,10 +1559,10 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="13">
@@ -3799,10 +1576,10 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="14">
@@ -3816,10 +1593,10 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="15">
@@ -3833,10 +1610,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="16">
@@ -3850,10 +1627,10 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="17">
@@ -3867,10 +1644,10 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="18">
@@ -3884,10 +1661,10 @@
         <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="19">
@@ -3901,10 +1678,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="20">
@@ -3918,10 +1695,10 @@
         <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="21">
@@ -3935,10 +1712,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="22">
@@ -3952,10 +1729,10 @@
         <v>57</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>0.785714285714286</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="23">
@@ -3969,10 +1746,10 @@
         <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>0.785714285714286</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="24">
@@ -3986,10 +1763,10 @@
         <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>0.785714285714286</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="25">
@@ -4003,10 +1780,10 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>0.785714285714286</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="26">
@@ -4020,10 +1797,10 @@
         <v>61</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>0.785714285714286</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="27">
@@ -4037,10 +1814,10 @@
         <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>0.714285714285714</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="28">
@@ -4054,10 +1831,10 @@
         <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.714285714285714</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="29">
@@ -4071,10 +1848,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>0.714285714285714</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="30">
@@ -4088,10 +1865,10 @@
         <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>0.714285714285714</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="31">
@@ -4105,10 +1882,10 @@
         <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="32">
@@ -4122,10 +1899,10 @@
         <v>67</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>0.642857142857143</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
@@ -4139,10 +1916,10 @@
         <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
@@ -4156,10 +1933,10 @@
         <v>69</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>0.571428571428571</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="35">
@@ -4173,10 +1950,10 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>0.571428571428571</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="36">
@@ -4190,10 +1967,10 @@
         <v>71</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="37">
@@ -4207,10 +1984,10 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="38">
@@ -4224,10 +2001,10 @@
         <v>73</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="39">
@@ -4241,10 +2018,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="40">
@@ -4258,10 +2035,10 @@
         <v>75</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="41">
@@ -4275,10 +2052,10 @@
         <v>76</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>0.428571428571429</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="42">
@@ -4292,10 +2069,10 @@
         <v>77</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>0.428571428571429</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="43">
@@ -4309,10 +2086,10 @@
         <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="44">
@@ -4326,10 +2103,10 @@
         <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="45">
@@ -4343,10 +2120,10 @@
         <v>80</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>0.357142857142857</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="46">
@@ -4360,10 +2137,10 @@
         <v>81</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="47">
@@ -4377,10 +2154,10 @@
         <v>82</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="48">
@@ -4394,10 +2171,10 @@
         <v>83</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="49">
@@ -4411,10 +2188,10 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="50">
@@ -4428,10 +2205,10 @@
         <v>85</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="51">
@@ -4496,10 +2273,10 @@
         <v>89</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="55">
@@ -4513,10 +2290,10 @@
         <v>90</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="56">
@@ -4530,10 +2307,10 @@
         <v>91</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="57">
@@ -4547,10 +2324,10 @@
         <v>92</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="58">
@@ -4819,10 +2596,10 @@
         <v>108</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="74">
@@ -4836,10 +2613,10 @@
         <v>109</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="75">
@@ -4853,10 +2630,10 @@
         <v>110</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="76">
@@ -6437,91 +4214,6 @@
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="s">
-        <v>204</v>
-      </c>
-      <c r="D169" t="n">
-        <v>1</v>
-      </c>
-      <c r="E169" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="s">
-        <v>205</v>
-      </c>
-      <c r="D170" t="n">
-        <v>1</v>
-      </c>
-      <c r="E170" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="s">
-        <v>206</v>
-      </c>
-      <c r="D171" t="n">
-        <v>1</v>
-      </c>
-      <c r="E171" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="s">
-        <v>207</v>
-      </c>
-      <c r="D172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E172" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="s">
-        <v>208</v>
-      </c>
-      <c r="D173" t="n">
-        <v>1</v>
-      </c>
-      <c r="E173" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T3/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/d_1rm_ext/spls/c_data/results.xlsx
@@ -1049,7 +1049,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.390753830568083</v>
@@ -1057,10 +1057,18 @@
       <c r="I3" t="n">
         <v>-0.235683391109077</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.323383084577114</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.587064676616915</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.783851635721953</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.826292301722843</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1084,6 +1092,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.810732493060046</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.707961807024363</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.517050763072304</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0306924213556706</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.28606510372672</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.812930887044644</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.227557042566095</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.41469770112982</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.45107015102043</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.98152059892911</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.765148099828287</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.331617511242393</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-4.53979636262747</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.231637225572832</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.172018390439252</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.942641596060005</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.97613492862022</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.685170274137987</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.63815010734619</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.424847116331247</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.127974823831079</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.3689504256793</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.126437607402341</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.689244078501638</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.600363942626769</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.844788527236501</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.353483190874283</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.979741790090465</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.180324734819296</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.94299786029856</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.0477398376004</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.542101263004109</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.356425192139768</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-2.36204514865091</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-1.84611611193458</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.45775252837975</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0167801603945985</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.65950894966236</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.432138257315768</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.356413704616672</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.81129892788429</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.52083461555224</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.016442435039281</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-1.18937365100082</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.728527309385144</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.745933455703841</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0475946132077637</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.913490190372135</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.0286646838154976</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.366357644895035</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-2.91026427823891</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.725541079685597</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.0745744646124877</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.0783015099870386</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.697872805114757</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.0407200210380372</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.371713471501684</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.62174602481955</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.0224687997945183</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.964809032304336</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.731667672614657</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-1.03534884334259</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.862231875134822</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.752717323576718</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.110731964456579</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.0159066589561595</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.953235063910343</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.874720377174834</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.085209147259941</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.0405633511564477</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.0949156237531085</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.627768252860689</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.349189235905384</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.463942734208049</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.991348225771532</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1.93356624676286</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.485753777581378</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.370732463976275</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.984936657993111</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.222449050201552</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.814042846139049</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.266816274436291</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.41148120306739</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.527325523291667</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-2.29697489879907</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.649365233082793</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.88721503706814</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.327931898403901</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.106311043663678</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.375253552191716</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.865576744387786</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.701146061447546</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.0742611588869702</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.3475185294501</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-2.57174058174963</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-1.51165631008844</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.0923687695168725</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-1.09177789012006</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.813085726875574</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.46843173010464</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.517184831471</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-1.82682679287831</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.143773532454364</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-2.40886108482543</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.418900643131412</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.179386505302511</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-1.63000357227393</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-2.06856038277154</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.9284993945202</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.58432174713901</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.953835716055851</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.199740766462082</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.51796207304983</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-1.56703376924691</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.814406090155577</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.0155733862524625</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-1.10721360581442</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.430548144247043</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.577683972533086</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.444180090787569</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.54787445221847</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-1.28321719097888</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.415413067890162</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.773276891134293</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.869014238342214</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-2.36544864381406</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.723920152128083</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-1.25550493607828</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-1.79431990785192</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.513113717740963</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.888898472949963</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-1.25169994536256</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-2.52126346300236</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.26467084323418</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.708272759162544</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-1.2458221624703</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.622505619456801</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.90790828364692</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.232469488246741</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-1.10710703335005</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.284285136072632</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-2.57098457967034</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-2.18004833382949</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-2.82019137059679</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.60819032134687</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.994535678986407</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.732876272999306</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.2205358452232</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.409142894036965</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.0568678234055529</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.577087123125823</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-1.90929291439135</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.0184933853537783</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.660953050451824</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.236685921761886</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.72147099820334</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.467650940032536</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.610264644720119</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-1.75157099388583</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.687926822521697</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-1.25881430062378</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.360688603841062</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.584417028013767</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-1.23076743488722</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-4.2572337010268</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.970082280692713</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.785312259946051</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.393265516725154</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.724047459180956</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.278573798954352</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.74000215114923</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.199576999312946</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.314907676184534</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.643258711451177</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.608841236534308</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-1.34448881150536</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1.41204472068064</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.43942186259604</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.701380412445954</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.234202056379868</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.49429553879122</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1.2803274920152</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-1.15386024351601</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.541023580309294</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.0617879648241811</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.00519530535722001</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.44959479444755</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.652571136168996</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-1.36210207104529</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.891893385618935</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.743005278163942</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.987989694021395</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.750909881664207</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.186075768619985</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-1.51492376798356</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.949645306680665</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.919729973441529</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.511756120402553</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.473575859594085</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.440087756233751</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
